--- a/reference_results/supplementary_tables/Supplementary_Table_S6_variance_components_heritability.xlsx
+++ b/reference_results/supplementary_tables/Supplementary_Table_S6_variance_components_heritability.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>'190_genotype_corrected' = dataset used throughout the manuscript (Table 1, M1-M4, GWAS). '190_genotype_REML_full' = complete REML variance-component output for the 190-genotype models. '209_genotype_original' = all originally phenotyped individuals, provided only to document the correction described in the response to Reviewer 2.</t>
+          <t>'190_genotype_corrected' = dataset used throughout the manuscript (Table 1, M1-M4, GWAS). '190_genotype_REML_full' = complete REML variance-component output for the 190-genotype models. '209_genotype_original' = all originally phenotyped individuals, provided only to document the correction to Table 1.</t>
         </is>
       </c>
     </row>
